--- a/business_forms/045_intern_feedback_form--business_forms.xlsx
+++ b/business_forms/045_intern_feedback_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>supervisor_name</t>
+          <t>supervisor name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>supervisor_email</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>supervisor_department</t>
+          <t>intern_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>supervisor_department</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>intern_name</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>intern_name</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>quality_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,58 +635,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quality_rating</t>
+          <t>improvement_suggestions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quality_rating</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>improvement_suggestions</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>improvement_suggestions</t>
+          <t>submission date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>intern_feedback_form_10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>intern performance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>intern_feedback_form_10</t>
+          <t>intern_feedback_form_11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>intern_feedback_form_10</t>
+          <t>communication skills</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>intern_feedback_form_11</t>
+          <t>intern_feedback_form_12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>intern_feedback_form_11</t>
+          <t>work ethic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,64 +773,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>intern_feedback_form_12</t>
+          <t>intern_feedback_form_13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>intern_feedback_form_12</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>intern_feedback_form_13</t>
+          <t>supervisor_feedback</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>intern_feedback_form_13</t>
+          <t>supervisor feedback</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intern_feedback_form_14</t>
+          <t>has_additional_feedback</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>intern_feedback_form_14</t>
+          <t>additional feedback</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>supervisor_feedback</t>
+          <t>submission_comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>supervisor_feedback</t>
+          <t>submission comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,108 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>has_additional_feedback</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>has_additional_feedback</t>
+          <t>submitted by</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submission_comments</t>
+          <t>has_internship_agreement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>submission_comments</t>
+          <t>has internship agreement</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>has_interview_questions</t>
+          <t>submission_status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>has_interview_questions</t>
+          <t>submission status</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submitted_by_intern</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>submitted_by_intern</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>has_internship_agreement</t>
+          <t>submission_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>has_internship_agreement</t>
+          <t>Submission Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>intern_is_performing_well</t>
+          <t>performing_well</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Intern is performing well</t>
+          <t>performing well</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>intern_is_performing_adequately</t>
+          <t>performing_average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Intern is performing adequately</t>
+          <t>performing average</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intern_is_performing_poorly</t>
+          <t>performing_poorly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Intern is performing poorly</t>
+          <t>performing poorly</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>communication_skills_are_excellent</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Communication skills are excellent</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>communication_skills_are_average</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Communication skills are average</t>
+          <t>average</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1101,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>communication_skills_are_below_average</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Communication skills are below average</t>
+          <t>below average</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>intern_feedback_form_11_choices</t>
+          <t>intern_feedback_form_12_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no_feedback</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No feedback</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>work_ethic_is_excellent</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Work ethic is excellent</t>
+          <t>average</t>
         </is>
       </c>
     </row>
@@ -1267,46 +1152,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>work_ethic_is_average</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Work ethic is average</t>
+          <t>below average</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>intern_feedback_form_12_choices</t>
+          <t>intern_feedback_form_13_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>work_ethic_is_below_average</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Work ethic is below average</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>intern_feedback_form_12_choices</t>
+          <t>intern_feedback_form_13_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no_feedback</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No feedback</t>
+          <t>average</t>
         </is>
       </c>
     </row>
@@ -1318,301 +1203,148 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>professionalism_is_excellent</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Professionalism is excellent</t>
+          <t>below average</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>intern_feedback_form_13_choices</t>
+          <t>has_additional_feedback_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>professionalism_is_average</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Professionalism is average</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>intern_feedback_form_13_choices</t>
+          <t>has_additional_feedback_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>professionalism_is_below_average</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Professionalism is below average</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>intern_feedback_form_13_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no_feedback</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No feedback</t>
+          <t>intern</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>intern_feedback_form_14_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>teamwork_is_excellent</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teamwork is excellent</t>
+          <t>supervisor</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>intern_feedback_form_14_choices</t>
+          <t>has_internship_agreement_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>teamwork_is_average</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Teamwork is average</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>intern_feedback_form_14_choices</t>
+          <t>has_internship_agreement_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>teamwork_is_below_average</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Teamwork is below average</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>intern_feedback_form_14_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no_feedback</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No feedback</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>has_additional_feedback_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>has_additional_feedback_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>has_interview_questions_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>has_interview_questions_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>submitted_by_intern_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>intern</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>submitted_by_intern_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>supervisor</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>has_internship_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>has_internship_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
           <t>submitted</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Submitted</t>
         </is>
       </c>
     </row>
